--- a/Docs/Economy/GOLFIN_Economy_Model.xlsx
+++ b/Docs/Economy/GOLFIN_Economy_Model.xlsx
@@ -14,8 +14,9 @@
     <sheet name="LevelUpCosts" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Progression" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="ClubEconomy" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Tournaments" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="PaidTrack" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="CharacterEconomy" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Tournaments" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="PaidTrack" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="160">
   <si>
     <t xml:space="preserve">GOLFIN Economy Model</t>
   </si>
@@ -284,6 +285,18 @@
     <t xml:space="preserve">gacha_banners.csv — prize pool is a STATIC MOCK (GachaMockPrizePool.cs), no real ticket spend</t>
   </si>
   <si>
+    <t xml:space="preserve">Character unlocks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200–6,000 (proposed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLANNED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">starter-selection flow shipped (pick James or Olivia; rest locked incl. the unpicked starter) — unlock pricing on CharacterEconomy tab, unlock purchase flow not built yet</t>
+  </si>
+  <si>
     <t xml:space="preserve">⚠ Only entry fees, level-ups and stamina boosts recur as live sinks today. Repairs, ball consumption and gacha are DESIGNED sinks awaiting mechanics — the economy currently leaks upward once a player caps their roster.</t>
   </si>
   <si>
@@ -375,6 +388,63 @@
   </si>
   <si>
     <t xml:space="preserve">Recommendation: shop stocks a rotating subset; Supreme optionally earn-only (tournament prizes) to keep scarcity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHARACTER UNLOCKS (starter flow 2026-08-20: player picks James OR Olivia; all others locked, incl. the unpicked starter)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proposed unlock RP (edit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days to unlock (net)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Characters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James*, Mike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olivia*, Ean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elizabeth, Camila, Johan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Richard, Guillermo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shae, Roshana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full roster cost (all 12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* = starter option (one is free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minus free starter (James)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if the player started as James</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minus free starter (Olivia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if the player started as Olivia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compounding sink: each unlocked character has its OWN level track (up to 14,520 RP to its cap band) — the roster multiplies long-term level-up demand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠ Starter asymmetry: James is Common, Olivia is Uncommon (different caps, start level 10 vs 40) — decide if intended.</t>
   </si>
   <si>
     <t xml:space="preserve">PRIZE TABLES (tournament_prizes.csv) — pool math by formula</t>
@@ -1218,7 +1288,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -1362,18 +1432,32 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
+      <c r="A11" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>85</v>
-      </c>
+      <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1396,13 +1480,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4073,7 +4157,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4082,27 +4166,27 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C3" s="2" t="n">
         <f aca="false">SUMIFS(LevelUpCosts!B:B,LevelUpCosts!A:A,"&gt;=10",LevelUpCosts!A:A,"&lt;=39")</f>
@@ -4119,10 +4203,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C4" s="2" t="n">
         <f aca="false">SUMIFS(LevelUpCosts!B:B,LevelUpCosts!A:A,"&gt;=40",LevelUpCosts!A:A,"&lt;=79")</f>
@@ -4139,10 +4223,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C5" s="2" t="n">
         <f aca="false">SUMIFS(LevelUpCosts!B:B,LevelUpCosts!A:A,"&gt;=80",LevelUpCosts!A:A,"&lt;=119")</f>
@@ -4159,10 +4243,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2" t="n">
         <f aca="false">SUMIFS(LevelUpCosts!B:B,LevelUpCosts!A:A,"&gt;=120",LevelUpCosts!A:A,"&lt;=159")</f>
@@ -4179,10 +4263,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C7" s="2" t="n">
         <f aca="false">SUMIFS(LevelUpCosts!B:B,LevelUpCosts!A:A,"&gt;=160",LevelUpCosts!A:A,"&lt;=199")</f>
@@ -4199,10 +4283,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C8" s="2" t="n">
         <f aca="false">SUMIFS(LevelUpCosts!B:B,LevelUpCosts!A:A,"&gt;=200",LevelUpCosts!A:A,"&lt;=239")</f>
@@ -4219,7 +4303,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="n">
@@ -4244,7 +4328,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -4279,7 +4363,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4288,16 +4372,16 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>23</v>
@@ -4305,7 +4389,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>100</v>
@@ -4321,7 +4405,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>200</v>
@@ -4337,7 +4421,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>400</v>
@@ -4353,7 +4437,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>800</v>
@@ -4369,7 +4453,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>1500</v>
@@ -4385,7 +4469,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B8" s="5" t="n">
         <v>3000</v>
@@ -4408,7 +4492,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -4417,7 +4501,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -4440,340 +4524,225 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="44"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>1</v>
+        <v>99</v>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <f aca="false">B3/Sources!B22</f>
+        <v>0.8</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <f aca="false">C3-B3+1</f>
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <f aca="false">D3*E3</f>
-        <v>300</v>
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B4" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>400</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <f aca="false">B4/Sources!B22</f>
+        <v>1.6</v>
+      </c>
+      <c r="D4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <f aca="false">C4-B4+1</f>
-        <v>2</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <f aca="false">D4*E4</f>
-        <v>300</v>
+      <c r="E4" s="2" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>10</v>
+        <v>103</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>800</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <f aca="false">B5/Sources!B22</f>
+        <v>3.2</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <f aca="false">C5-B5+1</f>
-        <v>7</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <f aca="false">D5*E5</f>
-        <v>350</v>
+        <v>3</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>1</v>
+        <v>105</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <f aca="false">B6/Sources!B22</f>
+        <v>6.4</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>500</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <f aca="false">C6-B6+1</f>
-        <v>1</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <f aca="false">D6*E6</f>
-        <v>500</v>
+        <v>2</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B7" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <f aca="false">B7/Sources!B22</f>
+        <v>12</v>
+      </c>
+      <c r="D7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <f aca="false">C7-B7+1</f>
-        <v>2</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <f aca="false">D7*E7</f>
-        <v>600</v>
+      <c r="E7" s="2" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>10</v>
+        <v>109</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <f aca="false">B8/Sources!B22</f>
+        <v>24</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <f aca="false">C8-B8+1</f>
-        <v>7</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <f aca="false">D8*E8</f>
-        <v>700</v>
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>124</v>
+      <c r="A9" s="3" t="s">
+        <v>131</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>1</v>
-      </c>
+        <f aca="false">SUMPRODUCT(B3:B8,D3:D8)</f>
+        <v>18800</v>
+      </c>
+      <c r="C9" s="2"/>
       <c r="D9" s="2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <f aca="false">C9-B9+1</f>
-        <v>1</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <f aca="false">D9*E9</f>
-        <v>2000</v>
+        <f aca="false">SUM(D3:D8)</f>
+        <v>12</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <f aca="false">C10-B10+1</f>
-        <v>2</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <f aca="false">D10*E10</f>
-        <v>2400</v>
+        <f aca="false">B9-B3</f>
+        <v>18600</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <f aca="false">B10/Sources!B22</f>
+        <v>74.4</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>500</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <f aca="false">C11-B11+1</f>
-        <v>7</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <f aca="false">D11*E11</f>
-        <v>3500</v>
+        <f aca="false">B9-B4</f>
+        <v>18400</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <f aca="false">B11/Sources!B22</f>
+        <v>73.6</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <f aca="false">C12-B12+1</f>
-        <v>40</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <f aca="false">D12*E12</f>
-        <v>4000</v>
-      </c>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
+      <c r="A13" s="2" t="s">
+        <v>137</v>
+      </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
-        <v>125</v>
+      <c r="A14" s="2" t="s">
+        <v>138</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2" t="n">
-        <f aca="false">SUMIFS(F3:F12,A3:A12,"prize_small")</f>
-        <v>950</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2" t="n">
-        <f aca="false">SUMIFS(F3:F12,A3:A12,"prize_medium")</f>
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2" t="n">
-        <f aca="false">SUMIFS(F3:F12,A3:A12,"prize_major")</f>
-        <v>11900</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2" t="n">
-        <f aca="false">MAX(D3:D12)</f>
-        <v>2000</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F18" s="2" t="str">
-        <f aca="false">IF(D18&lt;=2000,"OK","OVER CAP")</f>
-        <v>OK</v>
-      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4791,6 +4760,357 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <f aca="false">C3-B3+1</f>
+        <v>1</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <f aca="false">D3*E3</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <f aca="false">C4-B4+1</f>
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <f aca="false">D4*E4</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <f aca="false">C5-B5+1</f>
+        <v>7</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <f aca="false">D5*E5</f>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <f aca="false">C6-B6+1</f>
+        <v>1</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <f aca="false">D6*E6</f>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <f aca="false">C7-B7+1</f>
+        <v>2</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <f aca="false">D7*E7</f>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <f aca="false">C8-B8+1</f>
+        <v>7</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <f aca="false">D8*E8</f>
+        <v>700</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <f aca="false">C9-B9+1</f>
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <f aca="false">D9*E9</f>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <f aca="false">C10-B10+1</f>
+        <v>2</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <f aca="false">D10*E10</f>
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <f aca="false">C11-B11+1</f>
+        <v>7</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <f aca="false">D11*E11</f>
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <f aca="false">C12-B12+1</f>
+        <v>40</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <f aca="false">D12*E12</f>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2" t="n">
+        <f aca="false">SUMIFS(F3:F12,A3:A12,"prize_small")</f>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2" t="n">
+        <f aca="false">SUMIFS(F3:F12,A3:A12,"prize_medium")</f>
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2" t="n">
+        <f aca="false">SUMIFS(F3:F12,A3:A12,"prize_major")</f>
+        <v>11900</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2" t="n">
+        <f aca="false">MAX(D3:D12)</f>
+        <v>2000</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F18" s="2" t="str">
+        <f aca="false">IF(D18&lt;=2000,"OK","OVER CAP")</f>
+        <v>OK</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:A9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -4799,47 +5119,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
